--- a/entertainment_forms/004_studio_a_dance_center_registration_form--entertainment_forms.xlsx
+++ b/entertainment_forms/004_studio_a_dance_center_registration_form--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1014,8 +1014,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'full',_'value':_'full'}</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Full', 'value': 'Full'}</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'drop-in',_'value':_'drop-in'}</t>
+          <t>drop-in</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Drop-in', 'value': 'Drop-in'}</t>
+          <t>Drop-in</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'session',_'value':_'session'}</t>
+          <t>session</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Session', 'value': 'Session'}</t>
+          <t>Session</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'visa',_'value':_'visa'}</t>
+          <t>visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Visa', 'value': 'Visa'}</t>
+          <t>Visa</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'mastercard',_'value':_'mastercard'}</t>
+          <t>mastercard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Mastercard', 'value': 'Mastercard'}</t>
+          <t>Mastercard</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'amex',_'value':_'amex'}</t>
+          <t>amex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Amex', 'value': 'Amex'}</t>
+          <t>Amex</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'discover',_'value':_'discover'}</t>
+          <t>discover</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Discover', 'value': 'Discover'}</t>
+          <t>Discover</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'full_time',_'value':_'full-time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Full Time', 'value': 'full-time'}</t>
+          <t>Full Time</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'part_time',_'value':_'part-time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Part Time', 'value': 'part-time'}</t>
+          <t>Part Time</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'private',_'value':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Private', 'value': 'private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'trial',_'value':_'trial'}</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Trial', 'value': 'trial'}</t>
+          <t>Trial</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'beginner',_'value':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Beginner', 'value': 'beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'intermediate',_'value':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Intermediate', 'value': 'intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'advanced',_'value':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced', 'value': 'advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'ballet',_'value':_'ballet'}</t>
+          <t>ballet</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Ballet', 'value': 'ballet'}</t>
+          <t>Ballet</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'jazz',_'value':_'jazz'}</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Jazz', 'value': 'jazz'}</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'tap',_'value':_'tap'}</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Tap', 'value': 'tap'}</t>
+          <t>Tap</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'hip_hop',_'value':_'hip-hop'}</t>
+          <t>hip_hop</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Hip Hop', 'value': 'hip-hop'}</t>
+          <t>Hip Hop</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'paid',_'value':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Paid', 'value': 'paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'unpaid',_'value':_'unpaid'}</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Unpaid', 'value': 'unpaid'}</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'partially_paid',_'value':_'partially-paid'}</t>
+          <t>partially_paid</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Partially Paid', 'value': 'partially-paid'}</t>
+          <t>Partially Paid</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Active', 'value': 'active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'canceled',_'value':_'canceled'}</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Canceled', 'value': 'canceled'}</t>
+          <t>Canceled</t>
         </is>
       </c>
     </row>
